--- a/fixtures/files/intelliplan_konsulter_MBAB.xlsx
+++ b/fixtures/files/intelliplan_konsulter_MBAB.xlsx
@@ -456,10 +456,10 @@
         <v>Abdi Yilmaz</v>
       </c>
       <c r="C6" t="str">
-        <v>19651215-8657</v>
+        <v>19651215-9978</v>
       </c>
       <c r="D6" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E6" t="str">
         <v>MBAB / Uppsala</v>
@@ -479,7 +479,7 @@
         <v>Omar Nilsson</v>
       </c>
       <c r="C7" t="str">
-        <v>19780523-9337</v>
+        <v>19780523-9980</v>
       </c>
       <c r="D7" t="str">
         <v>Tillsvidareanställning</v>
@@ -502,10 +502,10 @@
         <v>Kerim Holm</v>
       </c>
       <c r="C8" t="str">
-        <v>19800513-2298</v>
+        <v>19800513-9848</v>
       </c>
       <c r="D8" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E8" t="str">
         <v>MBAB / Södertälje</v>
@@ -525,7 +525,7 @@
         <v>Ali Sjöberg</v>
       </c>
       <c r="C9" t="str">
-        <v>19960331-3777</v>
+        <v>19960331-9873</v>
       </c>
       <c r="D9" t="str">
         <v>Behovsanställning</v>
@@ -548,7 +548,7 @@
         <v>Sofia Yilmaz</v>
       </c>
       <c r="C10" t="str">
-        <v>19630404-0576</v>
+        <v>19630404-9817</v>
       </c>
       <c r="D10" t="str">
         <v>Behovsanställning</v>
@@ -571,7 +571,7 @@
         <v>Selma Mohamed</v>
       </c>
       <c r="C11" t="str">
-        <v>19641201-4828</v>
+        <v>19641201-9892</v>
       </c>
       <c r="D11" t="str">
         <v>Tillsvidareanställning</v>
@@ -594,7 +594,7 @@
         <v>Leila Nyström</v>
       </c>
       <c r="C12" t="str">
-        <v>20021119-9351</v>
+        <v>20021119-9989</v>
       </c>
       <c r="D12" t="str">
         <v>Provanställning</v>
@@ -617,7 +617,7 @@
         <v>Elin Hassan</v>
       </c>
       <c r="C13" t="str">
-        <v>19660709-8735</v>
+        <v>19660709-9972</v>
       </c>
       <c r="D13" t="str">
         <v>Tillsvidareanställning</v>
@@ -640,7 +640,7 @@
         <v>Omar Sandberg</v>
       </c>
       <c r="C14" t="str">
-        <v>19720108-1630</v>
+        <v>19720108-9831</v>
       </c>
       <c r="D14" t="str">
         <v>Tillsvidareanställning</v>
@@ -663,7 +663,7 @@
         <v>Elias Mattsson</v>
       </c>
       <c r="C15" t="str">
-        <v>19661104-6241</v>
+        <v>19661104-9922</v>
       </c>
       <c r="D15" t="str">
         <v>Tillsvidareanställning</v>
@@ -686,7 +686,7 @@
         <v>Axel Nordin</v>
       </c>
       <c r="C16" t="str">
-        <v>19690702-1288</v>
+        <v>19690702-9828</v>
       </c>
       <c r="D16" t="str">
         <v>Behovsanställning</v>
@@ -709,7 +709,7 @@
         <v>Axel Nordin</v>
       </c>
       <c r="C17" t="str">
-        <v>19690702-1288</v>
+        <v>19690702-9828</v>
       </c>
       <c r="D17" t="str">
         <v>Behovsanställning</v>
@@ -732,7 +732,7 @@
         <v>Mariam Nilsson</v>
       </c>
       <c r="C18" t="str">
-        <v>19900906-6623</v>
+        <v>19900906-9932</v>
       </c>
       <c r="D18" t="str">
         <v>Provanställning</v>
@@ -755,10 +755,10 @@
         <v>Amina Johansson</v>
       </c>
       <c r="C19" t="str">
-        <v>19851103-3980</v>
+        <v>19851103-9870</v>
       </c>
       <c r="D19" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E19" t="str">
         <v>MBAB / Södertälje</v>
@@ -778,10 +778,10 @@
         <v>Vera Yilmaz</v>
       </c>
       <c r="C20" t="str">
-        <v>19920615-0907</v>
+        <v>19920615-9817</v>
       </c>
       <c r="D20" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E20" t="str">
         <v>MBAB / Kungsängen</v>
@@ -801,10 +801,10 @@
         <v>Hugo Wallin</v>
       </c>
       <c r="C21" t="str">
-        <v>19890215-3439</v>
+        <v>19890215-9865</v>
       </c>
       <c r="D21" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E21" t="str">
         <v>MBAB / Kungsängen</v>
@@ -824,7 +824,7 @@
         <v>Aisha Axelsson</v>
       </c>
       <c r="C22" t="str">
-        <v>19971124-1415</v>
+        <v>19971124-9822</v>
       </c>
       <c r="D22" t="str">
         <v>Provanställning</v>
@@ -847,7 +847,7 @@
         <v>Yasmin Persson</v>
       </c>
       <c r="C23" t="str">
-        <v>19741010-0510</v>
+        <v>19741010-9818</v>
       </c>
       <c r="D23" t="str">
         <v>Tillsvidareanställning</v>
@@ -870,7 +870,7 @@
         <v>Isak Kaya</v>
       </c>
       <c r="C24" t="str">
-        <v>19950418-2792</v>
+        <v>19950418-9854</v>
       </c>
       <c r="D24" t="str">
         <v>Behovsanställning</v>
@@ -893,7 +893,7 @@
         <v>Karl Hansson</v>
       </c>
       <c r="C25" t="str">
-        <v>19660510-0731</v>
+        <v>19660510-9815</v>
       </c>
       <c r="D25" t="str">
         <v>Behovsanställning</v>
@@ -916,7 +916,7 @@
         <v>Mohammed Mohamed</v>
       </c>
       <c r="C26" t="str">
-        <v>19780804-6101</v>
+        <v>19780804-9923</v>
       </c>
       <c r="D26" t="str">
         <v>Tillsvidareanställning</v>
@@ -939,7 +939,7 @@
         <v>Agnes Söderberg</v>
       </c>
       <c r="C27" t="str">
-        <v>19670729-8409</v>
+        <v>19670729-9969</v>
       </c>
       <c r="D27" t="str">
         <v>Tillsvidareanställning</v>
@@ -962,10 +962,10 @@
         <v>Ebba Karlsson</v>
       </c>
       <c r="C28" t="str">
-        <v>19860608-1639</v>
+        <v>19860608-9830</v>
       </c>
       <c r="D28" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E28" t="str">
         <v>MBAB / Södertälje</v>
@@ -985,7 +985,7 @@
         <v>Ludvig Hansson</v>
       </c>
       <c r="C29" t="str">
-        <v>19740704-1206</v>
+        <v>19740704-9829</v>
       </c>
       <c r="D29" t="str">
         <v>Behovsanställning</v>
@@ -1008,7 +1008,7 @@
         <v>Emil Jönsson</v>
       </c>
       <c r="C30" t="str">
-        <v>19840119-7564</v>
+        <v>19840119-9958</v>
       </c>
       <c r="D30" t="str">
         <v>Behovsanställning</v>
@@ -1031,7 +1031,7 @@
         <v>Ludvig Ström</v>
       </c>
       <c r="C31" t="str">
-        <v>20031130-9363</v>
+        <v>20031130-9983</v>
       </c>
       <c r="D31" t="str">
         <v>Behovsanställning</v>
@@ -1054,10 +1054,10 @@
         <v>Abdi Olsson</v>
       </c>
       <c r="C32" t="str">
-        <v>19811123-6488</v>
+        <v>19811123-9920</v>
       </c>
       <c r="D32" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E32" t="str">
         <v>MBAB / Stockholm</v>
@@ -1077,7 +1077,7 @@
         <v>Elias Jakobsson</v>
       </c>
       <c r="C33" t="str">
-        <v>19640422-0482</v>
+        <v>19640422-9806</v>
       </c>
       <c r="D33" t="str">
         <v>Behovsanställning</v>
@@ -1100,10 +1100,10 @@
         <v>Freja Jonsson</v>
       </c>
       <c r="C34" t="str">
-        <v>19740417-2541</v>
+        <v>19740417-9850</v>
       </c>
       <c r="D34" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E34" t="str">
         <v>MBAB / Södertälje</v>
@@ -1120,7 +1120,7 @@
         <v>Amina Hansson</v>
       </c>
       <c r="C35" t="str">
-        <v>19770522-4678</v>
+        <v>19770522-9891</v>
       </c>
       <c r="D35" t="str">
         <v>Tillsvidareanställning</v>
@@ -1143,7 +1143,7 @@
         <v>Mohammed Nilsson</v>
       </c>
       <c r="C36" t="str">
-        <v>19940126-3372</v>
+        <v>19940126-9866</v>
       </c>
       <c r="D36" t="str">
         <v>Provanställning</v>
@@ -1166,10 +1166,10 @@
         <v>Freja Persson</v>
       </c>
       <c r="C37" t="str">
-        <v>20010421-8318</v>
+        <v>20010421-9969</v>
       </c>
       <c r="D37" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E37" t="str">
         <v>MBAB / Södertälje</v>
@@ -1189,10 +1189,10 @@
         <v>Sofia Larsson</v>
       </c>
       <c r="C38" t="str">
-        <v>19931109-6599</v>
+        <v>19931109-9932</v>
       </c>
       <c r="D38" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E38" t="str">
         <v>MBAB / Södertälje</v>
@@ -1212,7 +1212,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="C39" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="D39" t="str">
         <v>Behovsanställning</v>
@@ -1232,7 +1232,7 @@
         <v>Erik Öberg</v>
       </c>
       <c r="C40" t="str">
-        <v>20000305-8625</v>
+        <v>20000305-9979</v>
       </c>
       <c r="D40" t="str">
         <v>Provanställning</v>
@@ -1255,10 +1255,10 @@
         <v>Rania Ali</v>
       </c>
       <c r="C41" t="str">
-        <v>20050407-6928</v>
+        <v>20050407-9930</v>
       </c>
       <c r="D41" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E41" t="str">
         <v>MBAB / Stockholm</v>
@@ -1278,7 +1278,7 @@
         <v>Rania Magnusson</v>
       </c>
       <c r="C42" t="str">
-        <v>19700625-4333</v>
+        <v>19700625-9886</v>
       </c>
       <c r="D42" t="str">
         <v>Behovsanställning</v>
@@ -1301,7 +1301,7 @@
         <v>Ibrahim Bergström</v>
       </c>
       <c r="C43" t="str">
-        <v>19780727-3201</v>
+        <v>19780727-9869</v>
       </c>
       <c r="D43" t="str">
         <v>Tillsvidareanställning</v>
@@ -1324,10 +1324,10 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="C44" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="D44" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E44" t="str">
         <v>MBAB / Stockholm</v>
@@ -1344,7 +1344,7 @@
         <v>Ali Mattsson</v>
       </c>
       <c r="C45" t="str">
-        <v>19640701-9089</v>
+        <v>19640701-9980</v>
       </c>
       <c r="D45" t="str">
         <v>Tillsvidareanställning</v>
@@ -1367,7 +1367,7 @@
         <v>Wilma Öberg</v>
       </c>
       <c r="C46" t="str">
-        <v>19960319-8640</v>
+        <v>19960319-9978</v>
       </c>
       <c r="D46" t="str">
         <v>Behovsanställning</v>
@@ -1390,7 +1390,7 @@
         <v>Wilma Öberg</v>
       </c>
       <c r="C47" t="str">
-        <v>19960319-8640</v>
+        <v>19960319-9978</v>
       </c>
       <c r="D47" t="str">
         <v>Behovsanställning</v>
@@ -1413,7 +1413,7 @@
         <v>Agnes Gustafsson</v>
       </c>
       <c r="C48" t="str">
-        <v>19751229-6653</v>
+        <v>19751229-9939</v>
       </c>
       <c r="D48" t="str">
         <v>Tillsvidareanställning</v>
@@ -1436,10 +1436,10 @@
         <v>Klara Lundin</v>
       </c>
       <c r="C49" t="str">
-        <v>19790421-1252</v>
+        <v>19790421-9826</v>
       </c>
       <c r="D49" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E49" t="str">
         <v>MBAB / Stockholm</v>
@@ -1459,10 +1459,10 @@
         <v>Omar Hansson</v>
       </c>
       <c r="C50" t="str">
-        <v>19991014-8452</v>
+        <v>19991014-9963</v>
       </c>
       <c r="D50" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E50" t="str">
         <v>MBAB / Uppsala</v>
@@ -1482,10 +1482,10 @@
         <v>Ali Engström</v>
       </c>
       <c r="C51" t="str">
-        <v>19780918-0479</v>
+        <v>19780918-9801</v>
       </c>
       <c r="D51" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E51" t="str">
         <v>MBAB / Kungsängen</v>
@@ -1505,7 +1505,7 @@
         <v>Ebba Olsson</v>
       </c>
       <c r="C52" t="str">
-        <v>19830102-2060</v>
+        <v>19830102-9842</v>
       </c>
       <c r="D52" t="str">
         <v>Tillsvidareanställning</v>
@@ -1528,10 +1528,10 @@
         <v>Hassan Jönsson</v>
       </c>
       <c r="C53" t="str">
-        <v>19740202-4363</v>
+        <v>19740202-9883</v>
       </c>
       <c r="D53" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E53" t="str">
         <v>MBAB / Södertälje</v>
@@ -1548,7 +1548,7 @@
         <v>Kerim Axelsson</v>
       </c>
       <c r="C54" t="str">
-        <v>19900418-2136</v>
+        <v>19900418-9842</v>
       </c>
       <c r="D54" t="str">
         <v>Tillsvidareanställning</v>
@@ -1568,7 +1568,7 @@
         <v>Saga Axelsson</v>
       </c>
       <c r="C55" t="str">
-        <v>20001116-0587</v>
+        <v>20001116-9810</v>
       </c>
       <c r="D55" t="str">
         <v>Behovsanställning</v>
@@ -1591,7 +1591,7 @@
         <v>Dalia Söderberg</v>
       </c>
       <c r="C56" t="str">
-        <v>19790216-2556</v>
+        <v>19790216-9858</v>
       </c>
       <c r="D56" t="str">
         <v>Provanställning</v>
@@ -1614,7 +1614,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="C57" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="D57" t="str">
         <v>Tillsvidareanställning</v>
@@ -1634,7 +1634,7 @@
         <v>Hanna Lindqvist</v>
       </c>
       <c r="C58" t="str">
-        <v>20010219-3257</v>
+        <v>20010219-9866</v>
       </c>
       <c r="D58" t="str">
         <v>Behovsanställning</v>
@@ -1657,7 +1657,7 @@
         <v>Karl Pettersson</v>
       </c>
       <c r="C59" t="str">
-        <v>19710914-1130</v>
+        <v>19710914-9828</v>
       </c>
       <c r="D59" t="str">
         <v>Tillsvidareanställning</v>
@@ -1680,10 +1680,10 @@
         <v>Mariam Andersson</v>
       </c>
       <c r="C60" t="str">
-        <v>19781223-5302</v>
+        <v>19781223-9908</v>
       </c>
       <c r="D60" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E60" t="str">
         <v>MBAB / Stockholm</v>
@@ -1703,10 +1703,10 @@
         <v>Hiba Persson</v>
       </c>
       <c r="C61" t="str">
-        <v>19830312-8188</v>
+        <v>19830312-9962</v>
       </c>
       <c r="D61" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E61" t="str">
         <v>MBAB / Kungsängen</v>
@@ -1726,10 +1726,10 @@
         <v>Tilda Mohamed</v>
       </c>
       <c r="C62" t="str">
-        <v>19920109-0033</v>
+        <v>19920109-9802</v>
       </c>
       <c r="D62" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E62" t="str">
         <v>MBAB / Stockholm</v>
@@ -1749,10 +1749,10 @@
         <v>Tilda Sjöberg</v>
       </c>
       <c r="C63" t="str">
-        <v>20021221-0355</v>
+        <v>20021221-9802</v>
       </c>
       <c r="D63" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E63" t="str">
         <v>MBAB / Södertälje</v>
@@ -1772,7 +1772,7 @@
         <v>Oskar Lundin</v>
       </c>
       <c r="C64" t="str">
-        <v>19840316-2376</v>
+        <v>19840316-9843</v>
       </c>
       <c r="D64" t="str">
         <v>Behovsanställning</v>
@@ -1795,7 +1795,7 @@
         <v>Lucas Johansson</v>
       </c>
       <c r="C65" t="str">
-        <v>19910126-7236</v>
+        <v>19910126-9943</v>
       </c>
       <c r="D65" t="str">
         <v>Tillsvidareanställning</v>
@@ -1818,7 +1818,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="C66" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="D66" t="str">
         <v>Tillsvidareanställning</v>
@@ -1838,10 +1838,10 @@
         <v>Aisha Lundin</v>
       </c>
       <c r="C67" t="str">
-        <v>19870911-8635</v>
+        <v>19870911-9971</v>
       </c>
       <c r="D67" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E67" t="str">
         <v>MBAB / Södertälje</v>
@@ -1861,7 +1861,7 @@
         <v>Karl Ali</v>
       </c>
       <c r="C68" t="str">
-        <v>19891122-9634</v>
+        <v>19891122-9998</v>
       </c>
       <c r="D68" t="str">
         <v>Behovsanställning</v>
@@ -1884,7 +1884,7 @@
         <v>Karl Ali</v>
       </c>
       <c r="C69" t="str">
-        <v>19891122-9634</v>
+        <v>19891122-9998</v>
       </c>
       <c r="D69" t="str">
         <v>Behovsanställning</v>
@@ -1907,10 +1907,10 @@
         <v>Erik Axelsson</v>
       </c>
       <c r="C70" t="str">
-        <v>19720206-9394</v>
+        <v>19720206-9980</v>
       </c>
       <c r="D70" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E70" t="str">
         <v>MBAB / Uppsala</v>
@@ -1930,10 +1930,10 @@
         <v>Alva Eriksson</v>
       </c>
       <c r="C71" t="str">
-        <v>19890706-1876</v>
+        <v>19890706-9838</v>
       </c>
       <c r="D71" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E71" t="str">
         <v>MBAB / Stockholm</v>
@@ -1953,10 +1953,10 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="C72" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="D72" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E72" t="str">
         <v>MBAB / Södertälje</v>
@@ -1973,7 +1973,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="C73" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="D73" t="str">
         <v>Behovsanställning</v>
@@ -1996,7 +1996,7 @@
         <v>Agnes Nyström</v>
       </c>
       <c r="C74" t="str">
-        <v>19891229-9024</v>
+        <v>19891229-9982</v>
       </c>
       <c r="D74" t="str">
         <v>Tillsvidareanställning</v>
@@ -2016,7 +2016,7 @@
         <v>Oskar Åberg</v>
       </c>
       <c r="C75" t="str">
-        <v>19871203-6345</v>
+        <v>19871203-9927</v>
       </c>
       <c r="D75" t="str">
         <v>Behovsanställning</v>
@@ -2039,7 +2039,7 @@
         <v>Jonas Eriksson</v>
       </c>
       <c r="C76" t="str">
-        <v>19900101-7780</v>
+        <v>19900101-9950</v>
       </c>
       <c r="D76" t="str">
         <v>Tillsvidareanställning</v>
@@ -2062,7 +2062,7 @@
         <v>Jakob Axelsson</v>
       </c>
       <c r="C77" t="str">
-        <v>19861224-0575</v>
+        <v>19861224-9816</v>
       </c>
       <c r="D77" t="str">
         <v>Behovsanställning</v>
@@ -2085,10 +2085,10 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="C78" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="D78" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E78" t="str">
         <v>MBAB / Södertälje</v>
@@ -2105,7 +2105,7 @@
         <v>Viktor Axelsson</v>
       </c>
       <c r="C79" t="str">
-        <v>19931122-9232</v>
+        <v>19931122-9984</v>
       </c>
       <c r="D79" t="str">
         <v>Behovsanställning</v>
@@ -2128,7 +2128,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="C80" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="D80" t="str">
         <v>Tillsvidareanställning</v>
@@ -2148,10 +2148,10 @@
         <v>Isak Eriksson</v>
       </c>
       <c r="C81" t="str">
-        <v>20000208-0638</v>
+        <v>20000208-9811</v>
       </c>
       <c r="D81" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E81" t="str">
         <v>MBAB / Stockholm</v>
@@ -2171,10 +2171,10 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="C82" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="D82" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E82" t="str">
         <v>MBAB / Uppsala</v>
@@ -2191,10 +2191,10 @@
         <v>Gustav Jansson</v>
       </c>
       <c r="C83" t="str">
-        <v>19620430-2704</v>
+        <v>19620430-9857</v>
       </c>
       <c r="D83" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E83" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2214,7 +2214,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="C84" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="D84" t="str">
         <v>Tillsvidareanställning</v>
@@ -2234,10 +2234,10 @@
         <v>Karl Andersson</v>
       </c>
       <c r="C85" t="str">
-        <v>19841209-1012</v>
+        <v>19841209-9825</v>
       </c>
       <c r="D85" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E85" t="str">
         <v>MBAB / Södertälje</v>
@@ -2257,7 +2257,7 @@
         <v>Isak Eklund</v>
       </c>
       <c r="C86" t="str">
-        <v>19740503-8196</v>
+        <v>19740503-9962</v>
       </c>
       <c r="D86" t="str">
         <v>Tillsvidareanställning</v>
@@ -2277,10 +2277,10 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="C87" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="D87" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E87" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2297,10 +2297,10 @@
         <v>Johan Eriksson</v>
       </c>
       <c r="C88" t="str">
-        <v>19801202-5980</v>
+        <v>19801202-9917</v>
       </c>
       <c r="D88" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E88" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2320,10 +2320,10 @@
         <v>Kerim Nilsson</v>
       </c>
       <c r="C89" t="str">
-        <v>19830717-1044</v>
+        <v>19830717-9823</v>
       </c>
       <c r="D89" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E89" t="str">
         <v>MBAB / Uppsala</v>
@@ -2343,10 +2343,10 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="C90" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="D90" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E90" t="str">
         <v>MBAB / Södertälje</v>
@@ -2363,7 +2363,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="C91" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="D91" t="str">
         <v>Tillsvidareanställning</v>
@@ -2386,7 +2386,7 @@
         <v>Tilda Karlsson</v>
       </c>
       <c r="C92" t="str">
-        <v>19820816-4965</v>
+        <v>19820816-9899</v>
       </c>
       <c r="D92" t="str">
         <v>Tillsvidareanställning</v>
@@ -2406,7 +2406,7 @@
         <v>Freja Eklund</v>
       </c>
       <c r="C93" t="str">
-        <v>19900906-6508</v>
+        <v>19900906-9924</v>
       </c>
       <c r="D93" t="str">
         <v>Tillsvidareanställning</v>
@@ -2429,7 +2429,7 @@
         <v>Elin Nilsson</v>
       </c>
       <c r="C94" t="str">
-        <v>19830903-7524</v>
+        <v>19830903-9959</v>
       </c>
       <c r="D94" t="str">
         <v>Tillsvidareanställning</v>
@@ -2452,7 +2452,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="C95" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="D95" t="str">
         <v>Tillsvidareanställning</v>
@@ -2472,10 +2472,10 @@
         <v>Hanna Kaya</v>
       </c>
       <c r="C96" t="str">
-        <v>19731214-6470</v>
+        <v>19731214-9920</v>
       </c>
       <c r="D96" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E96" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2495,7 +2495,7 @@
         <v>Hassan Bengtsson</v>
       </c>
       <c r="C97" t="str">
-        <v>19751226-9692</v>
+        <v>19751226-9999</v>
       </c>
       <c r="D97" t="str">
         <v>Provanställning</v>
@@ -2518,10 +2518,10 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="C98" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="D98" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E98" t="str">
         <v>MBAB / Södertälje</v>
@@ -2538,7 +2538,7 @@
         <v>Dalia Bengtsson</v>
       </c>
       <c r="C99" t="str">
-        <v>19801013-6581</v>
+        <v>19801013-9932</v>
       </c>
       <c r="D99" t="str">
         <v>Tillsvidareanställning</v>
@@ -2561,7 +2561,7 @@
         <v>Lucas Larsson</v>
       </c>
       <c r="C100" t="str">
-        <v>19760909-8186</v>
+        <v>19760909-9960</v>
       </c>
       <c r="D100" t="str">
         <v>Behovsanställning</v>
@@ -2584,10 +2584,10 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="C101" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="D101" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E101" t="str">
         <v>MBAB / Södertälje</v>
@@ -2607,7 +2607,7 @@
         <v>Anna Svensson</v>
       </c>
       <c r="C102" t="str">
-        <v>19841204-9879</v>
+        <v>19841204-9994</v>
       </c>
       <c r="D102" t="str">
         <v>Behovsanställning</v>
@@ -2630,7 +2630,7 @@
         <v>Hassan Karlsson</v>
       </c>
       <c r="C103" t="str">
-        <v>20050925-7788</v>
+        <v>20050925-9958</v>
       </c>
       <c r="D103" t="str">
         <v>Tillsvidareanställning</v>
@@ -2653,10 +2653,10 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="C104" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="D104" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E104" t="str">
         <v>MBAB / Södertälje</v>
@@ -2673,10 +2673,10 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="C105" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="D105" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E105" t="str">
         <v>MBAB / Södertälje</v>
@@ -2693,7 +2693,7 @@
         <v>Ahmed Lindström</v>
       </c>
       <c r="C106" t="str">
-        <v>19950820-9666</v>
+        <v>19950820-9997</v>
       </c>
       <c r="D106" t="str">
         <v>Tillsvidareanställning</v>
@@ -2716,10 +2716,10 @@
         <v>Ludvig Bergström</v>
       </c>
       <c r="C107" t="str">
-        <v>19940909-8390</v>
+        <v>19940909-9968</v>
       </c>
       <c r="D107" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E107" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2739,7 +2739,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="C108" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="D108" t="str">
         <v>Tillsvidareanställning</v>
@@ -2762,7 +2762,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="C109" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="D109" t="str">
         <v>Provanställning</v>
@@ -2785,10 +2785,10 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="C110" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="D110" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E110" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2805,10 +2805,10 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="C111" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="D111" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E111" t="str">
         <v>MBAB / Södertälje</v>
@@ -2828,10 +2828,10 @@
         <v>Freja Lindqvist</v>
       </c>
       <c r="C112" t="str">
-        <v>19781207-5617</v>
+        <v>19781207-9916</v>
       </c>
       <c r="D112" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E112" t="str">
         <v>MBAB / Södertälje</v>
@@ -2848,10 +2848,10 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="C113" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="D113" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E113" t="str">
         <v>MBAB / Uppsala</v>
@@ -2868,10 +2868,10 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="C114" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="D114" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E114" t="str">
         <v>MBAB / Kungsängen</v>
@@ -2888,10 +2888,10 @@
         <v>Daniel Lindström</v>
       </c>
       <c r="C115" t="str">
-        <v>19671118-8877</v>
+        <v>19671118-9974</v>
       </c>
       <c r="D115" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E115" t="str">
         <v>MBAB / Stockholm</v>
@@ -2911,7 +2911,7 @@
         <v>Wilma Lindström</v>
       </c>
       <c r="C116" t="str">
-        <v>20030205-8177</v>
+        <v>20030205-9969</v>
       </c>
       <c r="D116" t="str">
         <v>Tillsvidareanställning</v>
@@ -2934,7 +2934,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="C117" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="D117" t="str">
         <v>Tillsvidareanställning</v>
@@ -2954,10 +2954,10 @@
         <v>Anna Jansson</v>
       </c>
       <c r="C118" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="D118" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E118" t="str">
         <v>MBAB / Stockholm</v>
@@ -2974,7 +2974,7 @@
         <v>Elias Magnusson</v>
       </c>
       <c r="C119" t="str">
-        <v>19961021-2293</v>
+        <v>19961021-9843</v>
       </c>
       <c r="D119" t="str">
         <v>Tillsvidareanställning</v>
@@ -2997,7 +2997,7 @@
         <v>Jakob Olsson</v>
       </c>
       <c r="C120" t="str">
-        <v>19880724-7211</v>
+        <v>19880724-9944</v>
       </c>
       <c r="D120" t="str">
         <v>Tillsvidareanställning</v>
@@ -3020,10 +3020,10 @@
         <v>Leila Forsberg</v>
       </c>
       <c r="C121" t="str">
-        <v>20051121-9719</v>
+        <v>20051121-9990</v>
       </c>
       <c r="D121" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E121" t="str">
         <v>MBAB / Stockholm</v>
@@ -3040,7 +3040,7 @@
         <v>Alva Öberg</v>
       </c>
       <c r="C122" t="str">
-        <v>20020617-3429</v>
+        <v>20020617-9863</v>
       </c>
       <c r="D122" t="str">
         <v>Tillsvidareanställning</v>
@@ -3063,7 +3063,7 @@
         <v>Fatima Gustafsson</v>
       </c>
       <c r="C123" t="str">
-        <v>19911106-0159</v>
+        <v>19911106-9804</v>
       </c>
       <c r="D123" t="str">
         <v>Tillsvidareanställning</v>
@@ -3086,7 +3086,7 @@
         <v>Elias Eklund</v>
       </c>
       <c r="C124" t="str">
-        <v>19940130-9415</v>
+        <v>19940130-9985</v>
       </c>
       <c r="D124" t="str">
         <v>Tillsvidareanställning</v>
@@ -3109,10 +3109,10 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="C125" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="D125" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E125" t="str">
         <v>MBAB / Stockholm</v>
@@ -3129,10 +3129,10 @@
         <v>Oskar Wallin</v>
       </c>
       <c r="C126" t="str">
-        <v>19830305-4392</v>
+        <v>19830305-9888</v>
       </c>
       <c r="D126" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E126" t="str">
         <v>MBAB / Uppsala</v>
@@ -3152,7 +3152,7 @@
         <v>Nadia Ali</v>
       </c>
       <c r="C127" t="str">
-        <v>19850909-5678</v>
+        <v>19850909-9910</v>
       </c>
       <c r="D127" t="str">
         <v>Behovsanställning</v>
@@ -3175,7 +3175,7 @@
         <v>Nadia Ali</v>
       </c>
       <c r="C128" t="str">
-        <v>19850909-5678</v>
+        <v>19850909-9910</v>
       </c>
       <c r="D128" t="str">
         <v>Behovsanställning</v>
@@ -3198,7 +3198,7 @@
         <v>Viktor Pettersson</v>
       </c>
       <c r="C129" t="str">
-        <v>19850227-1839</v>
+        <v>19850227-9832</v>
       </c>
       <c r="D129" t="str">
         <v>Behovsanställning</v>
@@ -3221,10 +3221,10 @@
         <v>Isak Sjöberg</v>
       </c>
       <c r="C130" t="str">
-        <v>19730829-7014</v>
+        <v>19730829-9945</v>
       </c>
       <c r="D130" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E130" t="str">
         <v>MBAB / Uppsala</v>
@@ -3244,7 +3244,7 @@
         <v>Omar Ahmed</v>
       </c>
       <c r="C131" t="str">
-        <v>19811109-0448</v>
+        <v>19811109-9803</v>
       </c>
       <c r="D131" t="str">
         <v>Provanställning</v>
@@ -3264,7 +3264,7 @@
         <v>Adam Holm</v>
       </c>
       <c r="C132" t="str">
-        <v>19740202-4728</v>
+        <v>19740202-9891</v>
       </c>
       <c r="D132" t="str">
         <v>Tillsvidareanställning</v>
@@ -3287,10 +3287,10 @@
         <v>Anna Nyström</v>
       </c>
       <c r="C133" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="D133" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E133" t="str">
         <v>MBAB / Södertälje</v>
@@ -3307,7 +3307,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="C134" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="D134" t="str">
         <v>Tillsvidareanställning</v>
@@ -3327,10 +3327,10 @@
         <v>Freja Wallin</v>
       </c>
       <c r="C135" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="D135" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E135" t="str">
         <v>MBAB / Kungsängen</v>
@@ -3350,10 +3350,10 @@
         <v>Abdi Åberg</v>
       </c>
       <c r="C136" t="str">
-        <v>19811012-7399</v>
+        <v>19811012-9940</v>
       </c>
       <c r="D136" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E136" t="str">
         <v>MBAB / Stockholm</v>
@@ -3370,10 +3370,10 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="C137" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="D137" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E137" t="str">
         <v>MBAB / Kungsängen</v>
@@ -3390,7 +3390,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="C138" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="D138" t="str">
         <v>Behovsanställning</v>
@@ -3410,10 +3410,10 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="C139" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="D139" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E139" t="str">
         <v>MBAB / Södertälje</v>
@@ -3430,7 +3430,7 @@
         <v>Ludvig Axelsson</v>
       </c>
       <c r="C140" t="str">
-        <v>19650609-6814</v>
+        <v>19650609-9933</v>
       </c>
       <c r="D140" t="str">
         <v>Provanställning</v>
@@ -3453,7 +3453,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="C141" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="D141" t="str">
         <v>Tillsvidareanställning</v>
@@ -3473,7 +3473,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="C142" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="D142" t="str">
         <v>Behovsanställning</v>
@@ -3493,10 +3493,10 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="C143" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="D143" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E143" t="str">
         <v>MBAB / Uppsala</v>
@@ -3513,7 +3513,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="C144" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="D144" t="str">
         <v>Tillsvidareanställning</v>
@@ -3533,10 +3533,10 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="C145" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="D145" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E145" t="str">
         <v>MBAB / Stockholm</v>
@@ -3553,7 +3553,7 @@
         <v>Jakob Svensson</v>
       </c>
       <c r="C146" t="str">
-        <v>19851119-7967</v>
+        <v>19851119-9955</v>
       </c>
       <c r="D146" t="str">
         <v>Provanställning</v>
@@ -3573,10 +3573,10 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="C147" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="D147" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E147" t="str">
         <v>MBAB / Stockholm</v>
@@ -3593,10 +3593,10 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="C148" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="D148" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E148" t="str">
         <v>MBAB / Södertälje</v>
@@ -3613,10 +3613,10 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="C149" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="D149" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E149" t="str">
         <v>MBAB / Stockholm</v>
@@ -3633,10 +3633,10 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="C150" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="D150" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E150" t="str">
         <v>MBAB / Stockholm</v>
@@ -3653,10 +3653,10 @@
         <v>Jonas Kaya</v>
       </c>
       <c r="C151" t="str">
-        <v>19890913-9399</v>
+        <v>19890913-9985</v>
       </c>
       <c r="D151" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E151" t="str">
         <v>MBAB / Kungsängen</v>
@@ -3676,10 +3676,10 @@
         <v>Filip Lindström</v>
       </c>
       <c r="C152" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="D152" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E152" t="str">
         <v>MBAB / Stockholm</v>
@@ -3696,7 +3696,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="C153" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="D153" t="str">
         <v>Provanställning</v>
@@ -3716,10 +3716,10 @@
         <v>Kerim Larsson</v>
       </c>
       <c r="C154" t="str">
-        <v>19721116-2610</v>
+        <v>19721116-9854</v>
       </c>
       <c r="D154" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E154" t="str">
         <v>MBAB / Kungsängen</v>
@@ -3736,10 +3736,10 @@
         <v>Agnes Hansson</v>
       </c>
       <c r="C155" t="str">
-        <v>19851123-0735</v>
+        <v>19851123-9819</v>
       </c>
       <c r="D155" t="str">
-        <v>Allmän visstidsanställning</v>
+        <v>Särskild visstidsanställning</v>
       </c>
       <c r="E155" t="str">
         <v>MBAB / Stockholm</v>
@@ -3756,7 +3756,7 @@
         <v>Johan Mattsson</v>
       </c>
       <c r="C156" t="str">
-        <v>19890413-1441</v>
+        <v>19890413-9824</v>
       </c>
       <c r="D156" t="str">
         <v>Tillsvidareanställning</v>
@@ -3776,7 +3776,7 @@
         <v>Linnea Nyström</v>
       </c>
       <c r="C157" t="str">
-        <v>19680118-2012</v>
+        <v>19680118-9843</v>
       </c>
       <c r="D157" t="str">
         <v>Behovsanställning</v>
